--- a/Daily_Report/Top 7 broker List with its Turnover 2024-01-31.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-01-31.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="271">
   <si>
     <t>Date: 2024-01-31</t>
   </si>
@@ -62,106 +62,106 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
     <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Bhrikuti Stock Broking Co. Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>Linch Stock Market Limited</t>
-  </si>
-  <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
+    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
+  </si>
+  <si>
     <t>58</t>
   </si>
   <si>
+    <t>45</t>
+  </si>
+  <si>
     <t>34</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
     <t>49</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
     <t>42</t>
   </si>
   <si>
-    <t>691,353,830.3</t>
-  </si>
-  <si>
-    <t>336,615,163.6</t>
-  </si>
-  <si>
-    <t>259,644,263.72</t>
-  </si>
-  <si>
-    <t>232,490,833.1</t>
-  </si>
-  <si>
-    <t>230,902,562.1</t>
-  </si>
-  <si>
-    <t>208,344,236.0</t>
-  </si>
-  <si>
-    <t>206,813,384.8</t>
-  </si>
-  <si>
-    <t>203,126,784.0</t>
-  </si>
-  <si>
-    <t>212,260,120.0</t>
-  </si>
-  <si>
-    <t>95,132,516.92</t>
-  </si>
-  <si>
-    <t>94,743,819.1</t>
-  </si>
-  <si>
-    <t>43,350,148.0</t>
-  </si>
-  <si>
-    <t>173,080,093.1</t>
-  </si>
-  <si>
-    <t>77,683,123.0</t>
-  </si>
-  <si>
-    <t>488,227,046.3</t>
-  </si>
-  <si>
-    <t>124,355,043.6</t>
-  </si>
-  <si>
-    <t>164,511,746.8</t>
-  </si>
-  <si>
-    <t>137,747,014.0</t>
-  </si>
-  <si>
-    <t>187,552,414.1</t>
-  </si>
-  <si>
-    <t>35,264,142.9</t>
-  </si>
-  <si>
-    <t>129,130,261.8</t>
+    <t>38</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>675,437,015.15</t>
+  </si>
+  <si>
+    <t>490,115,329.4</t>
+  </si>
+  <si>
+    <t>441,948,448.2</t>
+  </si>
+  <si>
+    <t>431,827,745.9</t>
+  </si>
+  <si>
+    <t>379,904,820.2</t>
+  </si>
+  <si>
+    <t>322,429,698.14</t>
+  </si>
+  <si>
+    <t>299,418,711.49</t>
+  </si>
+  <si>
+    <t>304,887,310.5</t>
+  </si>
+  <si>
+    <t>229,880,531.1</t>
+  </si>
+  <si>
+    <t>196,157,605.1</t>
+  </si>
+  <si>
+    <t>201,309,123.7</t>
+  </si>
+  <si>
+    <t>188,339,476.4</t>
+  </si>
+  <si>
+    <t>139,792,807.5</t>
+  </si>
+  <si>
+    <t>159,482,770.35</t>
+  </si>
+  <si>
+    <t>370,549,704.65</t>
+  </si>
+  <si>
+    <t>260,234,798.3</t>
+  </si>
+  <si>
+    <t>245,790,843.1</t>
+  </si>
+  <si>
+    <t>230,518,622.2</t>
+  </si>
+  <si>
+    <t>191,565,343.8</t>
+  </si>
+  <si>
+    <t>182,636,890.64</t>
+  </si>
+  <si>
+    <t>139,935,941.13</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,325 +179,322 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>RNLI</t>
-  </si>
-  <si>
-    <t>32,153,526.4</t>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>30,137,880.9</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>26,853,319.3</t>
   </si>
   <si>
     <t>NRN</t>
   </si>
   <si>
-    <t>18,729,679.0</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>16,110,087.4</t>
-  </si>
-  <si>
-    <t>HATHY</t>
-  </si>
-  <si>
-    <t>12,098,449.0</t>
+    <t>25,632,943.2</t>
   </si>
   <si>
     <t>PHCL</t>
   </si>
   <si>
-    <t>11,631,476.3</t>
+    <t>22,182,218.3</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>14,207,880.0</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>13,872,577.0</t>
+  </si>
+  <si>
+    <t>BARUN</t>
+  </si>
+  <si>
+    <t>13,486,667.0</t>
+  </si>
+  <si>
+    <t>12,881,043.9</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>10,354,501.6</t>
+  </si>
+  <si>
+    <t>SHL</t>
+  </si>
+  <si>
+    <t>9,708,631.0</t>
+  </si>
+  <si>
+    <t>15,491,426.0</t>
+  </si>
+  <si>
+    <t>11,956,220.3</t>
+  </si>
+  <si>
+    <t>UPCL</t>
+  </si>
+  <si>
+    <t>11,126,272.0</t>
+  </si>
+  <si>
+    <t>KSBBL</t>
+  </si>
+  <si>
+    <t>8,668,049.0</t>
+  </si>
+  <si>
+    <t>HURJA</t>
+  </si>
+  <si>
+    <t>7,904,290.7</t>
+  </si>
+  <si>
+    <t>32,189,629.0</t>
+  </si>
+  <si>
+    <t>15,592,029.7</t>
+  </si>
+  <si>
+    <t>SBL</t>
+  </si>
+  <si>
+    <t>11,898,772.2</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>9,152,326.4</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>8,223,935.3</t>
+  </si>
+  <si>
+    <t>18,892,962.39</t>
+  </si>
+  <si>
+    <t>CGH</t>
+  </si>
+  <si>
+    <t>12,385,089.0</t>
+  </si>
+  <si>
+    <t>NABIL</t>
+  </si>
+  <si>
+    <t>8,504,091.9</t>
   </si>
   <si>
     <t>SONA</t>
   </si>
   <si>
-    <t>61,683,492.0</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>51,109,042.8</t>
-  </si>
-  <si>
-    <t>39,197,646.0</t>
-  </si>
-  <si>
-    <t>3,303,444.0</t>
+    <t>6,663,430.0</t>
+  </si>
+  <si>
+    <t>SMJC</t>
+  </si>
+  <si>
+    <t>5,578,081.9</t>
+  </si>
+  <si>
+    <t>RFPL</t>
+  </si>
+  <si>
+    <t>16,424,336.0</t>
+  </si>
+  <si>
+    <t>7,939,882.4</t>
+  </si>
+  <si>
+    <t>SMHL</t>
+  </si>
+  <si>
+    <t>5,233,198.59</t>
+  </si>
+  <si>
+    <t>AKPL</t>
+  </si>
+  <si>
+    <t>4,867,177.7</t>
+  </si>
+  <si>
+    <t>MHL</t>
+  </si>
+  <si>
+    <t>4,586,389.59</t>
+  </si>
+  <si>
+    <t>17,394,070.5</t>
+  </si>
+  <si>
+    <t>9,473,280.0</t>
+  </si>
+  <si>
+    <t>SPDL</t>
+  </si>
+  <si>
+    <t>5,234,962.3</t>
+  </si>
+  <si>
+    <t>3,592,899.8</t>
+  </si>
+  <si>
+    <t>RADHI</t>
+  </si>
+  <si>
+    <t>3,246,177.3</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>74,913,348.8</t>
+  </si>
+  <si>
+    <t>35,133,178.9</t>
+  </si>
+  <si>
+    <t>18,808,941.39</t>
+  </si>
+  <si>
+    <t>13,854,414.4</t>
   </si>
   <si>
     <t>SHINE</t>
   </si>
   <si>
-    <t>2,959,884.0</t>
+    <t>13,375,834.5</t>
+  </si>
+  <si>
+    <t>34,120,561.79</t>
+  </si>
+  <si>
+    <t>27,708,263.3</t>
   </si>
   <si>
     <t>NIFRA</t>
   </si>
   <si>
-    <t>6,849,338.0</t>
-  </si>
-  <si>
-    <t>5,957,213.0</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>5,136,811.0</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>4,828,924.09</t>
-  </si>
-  <si>
-    <t>BARUN</t>
-  </si>
-  <si>
-    <t>3,788,650.0</t>
-  </si>
-  <si>
-    <t>11,248,237.7</t>
-  </si>
-  <si>
-    <t>9,561,842.19</t>
-  </si>
-  <si>
-    <t>HPPL</t>
-  </si>
-  <si>
-    <t>8,424,708.0</t>
-  </si>
-  <si>
-    <t>SCB</t>
-  </si>
-  <si>
-    <t>6,588,998.5</t>
-  </si>
-  <si>
-    <t>SBL</t>
-  </si>
-  <si>
-    <t>5,563,098.3</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>6,510,380.0</t>
-  </si>
-  <si>
-    <t>4,112,320.0</t>
-  </si>
-  <si>
-    <t>3,635,999.0</t>
-  </si>
-  <si>
-    <t>2,453,850.0</t>
-  </si>
-  <si>
-    <t>MBJC</t>
-  </si>
-  <si>
-    <t>1,989,444.0</t>
-  </si>
-  <si>
-    <t>131,011,642.8</t>
-  </si>
-  <si>
-    <t>4,536,445.0</t>
-  </si>
-  <si>
-    <t>SANIMA</t>
-  </si>
-  <si>
-    <t>3,251,724.8</t>
-  </si>
-  <si>
-    <t>2,917,794.0</t>
-  </si>
-  <si>
-    <t>ILBS</t>
-  </si>
-  <si>
-    <t>2,767,501.0</t>
-  </si>
-  <si>
-    <t>NABIL</t>
-  </si>
-  <si>
-    <t>5,808,670.0</t>
-  </si>
-  <si>
-    <t>EBL</t>
-  </si>
-  <si>
-    <t>4,290,524.0</t>
-  </si>
-  <si>
-    <t>4,210,869.59</t>
-  </si>
-  <si>
-    <t>IGI</t>
-  </si>
-  <si>
-    <t>3,205,495.0</t>
-  </si>
-  <si>
-    <t>CGH</t>
-  </si>
-  <si>
-    <t>3,084,830.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>177,167,722.5</t>
-  </si>
-  <si>
-    <t>138,774,531.5</t>
-  </si>
-  <si>
-    <t>35,403,997.0</t>
-  </si>
-  <si>
-    <t>MEL</t>
-  </si>
-  <si>
-    <t>16,820,927.6</t>
-  </si>
-  <si>
-    <t>7,908,106.6</t>
-  </si>
-  <si>
-    <t>27,742,233.5</t>
-  </si>
-  <si>
-    <t>19,529,609.2</t>
+    <t>20,455,901.89</t>
+  </si>
+  <si>
+    <t>16,300,089.0</t>
+  </si>
+  <si>
+    <t>11,394,210.2</t>
+  </si>
+  <si>
+    <t>29,851,194.4</t>
+  </si>
+  <si>
+    <t>24,967,223.6</t>
+  </si>
+  <si>
+    <t>6,909,873.9</t>
   </si>
   <si>
     <t>GBIME</t>
   </si>
   <si>
-    <t>6,576,615.2</t>
-  </si>
-  <si>
-    <t>3,703,738.8</t>
-  </si>
-  <si>
-    <t>HDHPC</t>
-  </si>
-  <si>
-    <t>3,072,567.9</t>
-  </si>
-  <si>
-    <t>23,200,152.0</t>
-  </si>
-  <si>
-    <t>20,757,778.2</t>
-  </si>
-  <si>
-    <t>RIDI</t>
-  </si>
-  <si>
-    <t>19,525,868.7</t>
-  </si>
-  <si>
-    <t>LEC</t>
-  </si>
-  <si>
-    <t>18,069,478.0</t>
-  </si>
-  <si>
-    <t>14,505,330.0</t>
-  </si>
-  <si>
-    <t>25,433,774.4</t>
-  </si>
-  <si>
-    <t>23,753,407.0</t>
-  </si>
-  <si>
-    <t>MAKAR</t>
-  </si>
-  <si>
-    <t>17,502,902.0</t>
-  </si>
-  <si>
-    <t>10,837,871.1</t>
-  </si>
-  <si>
-    <t>4,485,197.8</t>
-  </si>
-  <si>
-    <t>162,486,178.0</t>
-  </si>
-  <si>
-    <t>MSHL</t>
-  </si>
-  <si>
-    <t>5,570,580.0</t>
-  </si>
-  <si>
-    <t>1,933,326.0</t>
-  </si>
-  <si>
-    <t>1,518,824.0</t>
-  </si>
-  <si>
-    <t>CHL</t>
-  </si>
-  <si>
-    <t>1,486,800.0</t>
-  </si>
-  <si>
-    <t>3,150,990.0</t>
-  </si>
-  <si>
-    <t>3,017,581.0</t>
-  </si>
-  <si>
-    <t>2,963,776.0</t>
+    <t>5,920,210.4</t>
+  </si>
+  <si>
+    <t>5,531,637.2</t>
+  </si>
+  <si>
+    <t>40,270,890.0</t>
+  </si>
+  <si>
+    <t>18,036,108.2</t>
+  </si>
+  <si>
+    <t>17,146,732.1</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>9,328,734.79</t>
+  </si>
+  <si>
+    <t>NICA</t>
+  </si>
+  <si>
+    <t>8,547,482.5</t>
+  </si>
+  <si>
+    <t>15,679,817.0</t>
+  </si>
+  <si>
+    <t>10,158,547.0</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>6,271,779.4</t>
   </si>
   <si>
     <t>MEN</t>
   </si>
   <si>
-    <t>1,660,018.6</t>
-  </si>
-  <si>
-    <t>MKCL</t>
-  </si>
-  <si>
-    <t>1,608,088.0</t>
-  </si>
-  <si>
-    <t>ILI</t>
-  </si>
-  <si>
-    <t>11,543,272.4</t>
-  </si>
-  <si>
-    <t>9,969,173.5</t>
-  </si>
-  <si>
-    <t>MLBSL</t>
-  </si>
-  <si>
-    <t>8,740,714.0</t>
-  </si>
-  <si>
-    <t>CBBL</t>
-  </si>
-  <si>
-    <t>6,713,158.0</t>
-  </si>
-  <si>
-    <t>4,689,871.4</t>
+    <t>5,776,066.5</t>
+  </si>
+  <si>
+    <t>NWCL</t>
+  </si>
+  <si>
+    <t>5,079,816.0</t>
+  </si>
+  <si>
+    <t>18,428,416.3</t>
+  </si>
+  <si>
+    <t>9,514,497.19</t>
+  </si>
+  <si>
+    <t>8,720,814.1</t>
+  </si>
+  <si>
+    <t>UMHL</t>
+  </si>
+  <si>
+    <t>6,718,232.7</t>
+  </si>
+  <si>
+    <t>UNHPL</t>
+  </si>
+  <si>
+    <t>5,324,097.8</t>
+  </si>
+  <si>
+    <t>17,606,009.5</t>
+  </si>
+  <si>
+    <t>6,541,803.5</t>
+  </si>
+  <si>
+    <t>5,845,327.6</t>
+  </si>
+  <si>
+    <t>4,913,356.5</t>
+  </si>
+  <si>
+    <t>4,142,566.9</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -515,103 +512,103 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>567,125,553.2</t>
-  </si>
-  <si>
-    <t>233,786,791.5</t>
-  </si>
-  <si>
-    <t>227,475,310.6</t>
-  </si>
-  <si>
-    <t>159,847,143.69</t>
-  </si>
-  <si>
-    <t>135,660,924.5</t>
+    <t>638,782,691.5</t>
+  </si>
+  <si>
+    <t>260,172,364.4</t>
+  </si>
+  <si>
+    <t>242,648,304.3</t>
+  </si>
+  <si>
+    <t>198,948,160.5</t>
+  </si>
+  <si>
+    <t>117,440,159.5</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>1,488,184,577.2</t>
+    <t>1,812,127,199.7</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,421,033,343.7</t>
+    <t>1,799,265,664.6</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>203,318,185.9</t>
+    <t>394,093,203.2</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>239,536,904.1</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>218,585,695.2</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>163,281,097.6</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>112,588,480.8</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>104,063,244.3</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>99,779,474.5</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>77,848,212.5</t>
+    <t>137,210,534.9</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>120,875,526.6</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>112,660,623.9</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>73,405,476.0</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>48,295,377.2</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>42,620,674.6</t>
+    <t>109,945,679.5</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>40,366,792.4</t>
+    <t>99,642,255.7</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>27,671,534.6</t>
+    <t>72,353,946.09</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>7,356,620.51</t>
+    <t>11,866,237.98</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>1,258,940.0</t>
+    <t>4,160,488.4</t>
   </si>
   <si>
     <t>Total</t>
@@ -623,214 +620,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>77,986,262.9</t>
-  </si>
-  <si>
-    <t>76,627,710.4</t>
-  </si>
-  <si>
-    <t>24,675,748.9</t>
-  </si>
-  <si>
-    <t>8,407,458.6</t>
-  </si>
-  <si>
-    <t>6,410,917.5</t>
-  </si>
-  <si>
-    <t>126,628,448.7</t>
-  </si>
-  <si>
-    <t>62,338,802.9</t>
-  </si>
-  <si>
-    <t>6,182,996.6</t>
-  </si>
-  <si>
-    <t>4,256,334.2</t>
-  </si>
-  <si>
-    <t>2,545,637.2</t>
-  </si>
-  <si>
-    <t>34,915,443.9</t>
-  </si>
-  <si>
-    <t>21,996,032.3</t>
-  </si>
-  <si>
-    <t>10,808,747.7</t>
-  </si>
-  <si>
-    <t>5,799,117.0</t>
-  </si>
-  <si>
-    <t>4,973,372.09</t>
-  </si>
-  <si>
-    <t>32,267,835.5</t>
-  </si>
-  <si>
-    <t>27,322,891.2</t>
-  </si>
-  <si>
-    <t>14,550,491.2</t>
-  </si>
-  <si>
-    <t>12,654,775.9</t>
-  </si>
-  <si>
-    <t>1,762,206.5</t>
-  </si>
-  <si>
-    <t>18,160,051.8</t>
-  </si>
-  <si>
-    <t>8,645,591.0</t>
-  </si>
-  <si>
-    <t>6,059,502.0</t>
-  </si>
-  <si>
-    <t>2,130,660.5</t>
-  </si>
-  <si>
-    <t>1,885,719.0</t>
-  </si>
-  <si>
-    <t>142,519,259.0</t>
-  </si>
-  <si>
-    <t>12,433,526.4</t>
-  </si>
-  <si>
-    <t>4,522,796.09</t>
-  </si>
-  <si>
-    <t>4,436,421.7</t>
-  </si>
-  <si>
-    <t>3,519,379.6</t>
-  </si>
-  <si>
-    <t>26,441,292.7</t>
-  </si>
-  <si>
-    <t>21,583,490.5</t>
-  </si>
-  <si>
-    <t>12,045,935.8</t>
-  </si>
-  <si>
-    <t>3,679,845.0</t>
-  </si>
-  <si>
-    <t>3,186,040.6</t>
-  </si>
-  <si>
-    <t>350,251,821.6</t>
-  </si>
-  <si>
-    <t>93,511,675.6</t>
-  </si>
-  <si>
-    <t>16,069,717.5</t>
-  </si>
-  <si>
-    <t>11,438,670.1</t>
-  </si>
-  <si>
-    <t>2,858,852.9</t>
-  </si>
-  <si>
-    <t>74,189,230.09</t>
-  </si>
-  <si>
-    <t>26,981,710.6</t>
-  </si>
-  <si>
-    <t>6,189,851.2</t>
-  </si>
-  <si>
-    <t>4,361,526.9</t>
-  </si>
-  <si>
-    <t>3,608,936.4</t>
-  </si>
-  <si>
-    <t>62,412,125.0</t>
-  </si>
-  <si>
-    <t>59,476,184.3</t>
-  </si>
-  <si>
-    <t>15,375,017.9</t>
-  </si>
-  <si>
-    <t>7,735,389.0</t>
-  </si>
-  <si>
-    <t>7,076,646.0</t>
-  </si>
-  <si>
-    <t>59,860,087.1</t>
-  </si>
-  <si>
-    <t>47,118,592.6</t>
-  </si>
-  <si>
-    <t>11,937,505.4</t>
-  </si>
-  <si>
-    <t>5,063,467.59</t>
-  </si>
-  <si>
-    <t>4,106,934.0</t>
-  </si>
-  <si>
-    <t>173,907,782.1</t>
-  </si>
-  <si>
-    <t>6,791,973.0</t>
-  </si>
-  <si>
-    <t>2,359,679.4</t>
-  </si>
-  <si>
-    <t>1,276,870.0</t>
-  </si>
-  <si>
-    <t>1,089,356.2</t>
-  </si>
-  <si>
-    <t>11,763,140.0</t>
-  </si>
-  <si>
-    <t>9,752,010.8</t>
-  </si>
-  <si>
-    <t>3,176,203.0</t>
-  </si>
-  <si>
-    <t>2,525,519.29</t>
-  </si>
-  <si>
-    <t>2,199,221.6</t>
-  </si>
-  <si>
-    <t>55,757,660.9</t>
-  </si>
-  <si>
-    <t>31,556,871.4</t>
-  </si>
-  <si>
-    <t>18,715,181.3</t>
-  </si>
-  <si>
-    <t>5,039,115.8</t>
-  </si>
-  <si>
-    <t>4,234,015.0</t>
+    <t>134,036,390.2</t>
+  </si>
+  <si>
+    <t>95,671,806.0</t>
+  </si>
+  <si>
+    <t>27,823,787.6</t>
+  </si>
+  <si>
+    <t>14,100,374.5</t>
+  </si>
+  <si>
+    <t>6,189,220.1</t>
+  </si>
+  <si>
+    <t>100,592,252.5</t>
+  </si>
+  <si>
+    <t>53,601,763.0</t>
+  </si>
+  <si>
+    <t>13,293,541.6</t>
+  </si>
+  <si>
+    <t>11,449,750.6</t>
+  </si>
+  <si>
+    <t>11,060,660.0</t>
+  </si>
+  <si>
+    <t>69,646,938.0</t>
+  </si>
+  <si>
+    <t>58,748,752.5</t>
+  </si>
+  <si>
+    <t>19,296,122.6</t>
+  </si>
+  <si>
+    <t>14,321,107.5</t>
+  </si>
+  <si>
+    <t>12,655,910.4</t>
+  </si>
+  <si>
+    <t>83,341,243.7</t>
+  </si>
+  <si>
+    <t>46,718,412.5</t>
+  </si>
+  <si>
+    <t>27,807,434.5</t>
+  </si>
+  <si>
+    <t>18,571,108.7</t>
+  </si>
+  <si>
+    <t>5,185,396.4</t>
+  </si>
+  <si>
+    <t>63,312,080.1</t>
+  </si>
+  <si>
+    <t>59,823,532.6</t>
+  </si>
+  <si>
+    <t>19,089,144.1</t>
+  </si>
+  <si>
+    <t>13,047,372.1</t>
+  </si>
+  <si>
+    <t>7,310,317.1</t>
+  </si>
+  <si>
+    <t>58,251,384.3</t>
+  </si>
+  <si>
+    <t>41,692,659.2</t>
+  </si>
+  <si>
+    <t>11,024,373.7</t>
+  </si>
+  <si>
+    <t>4,310,405.8</t>
+  </si>
+  <si>
+    <t>4,114,068.5</t>
+  </si>
+  <si>
+    <t>59,178,653.4</t>
+  </si>
+  <si>
+    <t>58,744,381.5</t>
+  </si>
+  <si>
+    <t>10,982,161.5</t>
+  </si>
+  <si>
+    <t>6,636,460.7</t>
+  </si>
+  <si>
+    <t>6,124,276.2</t>
+  </si>
+  <si>
+    <t>179,540,109.9</t>
+  </si>
+  <si>
+    <t>89,380,235.8</t>
+  </si>
+  <si>
+    <t>23,582,433.2</t>
+  </si>
+  <si>
+    <t>18,225,315.2</t>
+  </si>
+  <si>
+    <t>15,198,686.5</t>
+  </si>
+  <si>
+    <t>86,900,953.4</t>
+  </si>
+  <si>
+    <t>72,886,575.2</t>
+  </si>
+  <si>
+    <t>26,841,303.3</t>
+  </si>
+  <si>
+    <t>19,178,460.5</t>
+  </si>
+  <si>
+    <t>17,115,129.2</t>
+  </si>
+  <si>
+    <t>109,596,505.9</t>
+  </si>
+  <si>
+    <t>73,047,266.2</t>
+  </si>
+  <si>
+    <t>13,005,761.0</t>
+  </si>
+  <si>
+    <t>12,060,437.9</t>
+  </si>
+  <si>
+    <t>7,508,007.4</t>
+  </si>
+  <si>
+    <t>79,679,838.7</t>
+  </si>
+  <si>
+    <t>74,678,257.8</t>
+  </si>
+  <si>
+    <t>20,107,512.2</t>
+  </si>
+  <si>
+    <t>14,723,252.7</t>
+  </si>
+  <si>
+    <t>9,733,219.69</t>
+  </si>
+  <si>
+    <t>62,613,090.9</t>
+  </si>
+  <si>
+    <t>60,101,295.3</t>
+  </si>
+  <si>
+    <t>14,608,720.3</t>
+  </si>
+  <si>
+    <t>10,274,232.9</t>
+  </si>
+  <si>
+    <t>9,857,904.3</t>
+  </si>
+  <si>
+    <t>78,107,803.7</t>
+  </si>
+  <si>
+    <t>59,032,603.7</t>
+  </si>
+  <si>
+    <t>9,207,860.4</t>
+  </si>
+  <si>
+    <t>8,973,624.5</t>
+  </si>
+  <si>
+    <t>5,227,006.09</t>
+  </si>
+  <si>
+    <t>49,850,834.8</t>
+  </si>
+  <si>
+    <t>48,529,512.9</t>
+  </si>
+  <si>
+    <t>11,514,669.7</t>
+  </si>
+  <si>
+    <t>6,414,212.6</t>
+  </si>
+  <si>
+    <t>4,689,716.59</t>
   </si>
 </sst>
 </file>
@@ -1639,7 +1636,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.04650806141631932</v>
+        <v>0.04461982423824822</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1648,52 +1645,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1832463259833967</v>
+        <v>0.02830471966053956</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.02637970083323819</v>
+        <v>0.03505256339985945</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L9" s="15" t="s">
         <v>81</v>
       </c>
       <c r="M9" s="16">
-        <v>0.0483814245491643</v>
+        <v>0.07454275299728952</v>
       </c>
       <c r="N9" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="O9" s="17" t="s">
-        <v>90</v>
-      </c>
       <c r="P9" s="18">
-        <v>0.02819535626105554</v>
+        <v>0.04973077833035611</v>
       </c>
       <c r="Q9" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="S9" s="16">
+        <v>0.05093927791002832</v>
+      </c>
+      <c r="T9" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="R9" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="S9" s="16">
-        <v>0.6288229773728897</v>
-      </c>
-      <c r="T9" s="17" t="s">
-        <v>103</v>
-      </c>
       <c r="U9" s="17" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="V9" s="18">
-        <v>0.02808652837250986</v>
+        <v>0.05809279725185421</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1705,7 +1702,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02709130719919872</v>
+        <v>0.03975695541950193</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1714,52 +1711,52 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1518322652295394</v>
+        <v>0.02751733355598243</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>74</v>
       </c>
       <c r="J10" s="14">
-        <v>0.02294374970834807</v>
+        <v>0.02705342749521165</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="L10" s="15" t="s">
         <v>82</v>
       </c>
       <c r="M10" s="16">
-        <v>0.04112782457916186</v>
+        <v>0.03610705853905623</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="O10" s="17" t="s">
         <v>91</v>
       </c>
       <c r="P10" s="18">
-        <v>0.01780976340236114</v>
+        <v>0.03260050502512681</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="S10" s="16">
-        <v>0.02177379651626167</v>
+        <v>0.02462515843237393</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="V10" s="18">
-        <v>0.02074587195673614</v>
+        <v>0.03163890443873074</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1771,16 +1768,16 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02330223207559193</v>
+        <v>0.03795016059981178</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
       <c r="G11" s="12">
-        <v>0.1164464653962487</v>
+        <v>0.02628165888173503</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>75</v>
@@ -1789,7 +1786,7 @@
         <v>76</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01978403422591892</v>
+        <v>0.02517549738055625</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>83</v>
@@ -1798,34 +1795,34 @@
         <v>84</v>
       </c>
       <c r="M11" s="16">
-        <v>0.03623673195052954</v>
+        <v>0.02755444112374253</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01574689759581494</v>
+        <v>0.02238479600106953</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01560746225779915</v>
+        <v>0.01623051049636168</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02036072086955176</v>
+        <v>0.01748375134589689</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1837,16 +1834,16 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01749964847197</v>
+        <v>0.03284128320251121</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" s="12">
-        <v>0.009813711196699042</v>
+        <v>0.02112666341751848</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>77</v>
@@ -1855,7 +1852,7 @@
         <v>78</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01859823140636569</v>
+        <v>0.0196132581419934</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>85</v>
@@ -1864,34 +1861,34 @@
         <v>86</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02834089590605884</v>
+        <v>0.02119439171497665</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01062720992648526</v>
+        <v>0.01753973533816194</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01400467829597167</v>
+        <v>0.01509531450755711</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01549945620347489</v>
+        <v>0.0119995833998504</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1903,16 +1900,16 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01682420171875339</v>
+        <v>0.02103509236437795</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G13" s="12">
-        <v>0.008793079813591618</v>
+        <v>0.01980887031606484</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>79</v>
@@ -1921,7 +1918,7 @@
         <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.0145916953670337</v>
+        <v>0.0178850966265255</v>
       </c>
       <c r="K13" s="15" t="s">
         <v>87</v>
@@ -1930,34 +1927,34 @@
         <v>88</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02392824794776822</v>
+        <v>0.01904448099521713</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P13" s="18">
-        <v>0.008615945972649733</v>
+        <v>0.01468284055217681</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01328330964721289</v>
+        <v>0.01422446389540884</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01491600750591264</v>
+        <v>0.01084159798780116</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1968,7 +1965,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1977,7 +1974,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1986,7 +1983,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -1995,7 +1992,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2004,7 +2001,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2013,7 +2010,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2022,7 +2019,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2031,67 +2028,67 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2562620104717167</v>
+        <v>0.1109109319147446</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G16" s="12">
-        <v>0.08241528160319632</v>
+        <v>0.06961741401104603</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J16" s="14">
-        <v>0.0893536089247826</v>
+        <v>0.06754451683579868</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L16" s="15" t="s">
         <v>133</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1093968913133892</v>
+        <v>0.09325683766815134</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P16" s="18">
-        <v>0.7037001951049378</v>
+        <v>0.04127301409796642</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="S16" s="16">
-        <v>0.01512396052079886</v>
+        <v>0.05715483532164684</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>153</v>
+        <v>62</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="V16" s="18">
-        <v>0.05581491938330289</v>
+        <v>0.05880063210608</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2100,151 +2097,151 @@
         <v>62</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D17" s="10">
-        <v>0.2007286651464438</v>
+        <v>0.05201547755299978</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G17" s="12">
-        <v>0.05801761569840343</v>
+        <v>0.05653416989409514</v>
       </c>
       <c r="H17" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.0564935202322541</v>
+      </c>
+      <c r="K17" s="15" t="s">
         <v>66</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="J17" s="14">
-        <v>0.07994699325375874</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>79</v>
       </c>
       <c r="L17" s="15" t="s">
         <v>134</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1021692196775048</v>
+        <v>0.04176690444568305</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>140</v>
+        <v>58</v>
       </c>
       <c r="O17" s="17" t="s">
         <v>141</v>
       </c>
       <c r="P17" s="18">
-        <v>0.0241252411811155</v>
+        <v>0.0267397160021609</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="S17" s="16">
-        <v>0.01448363083104445</v>
+        <v>0.02950874951931002</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="V17" s="18">
-        <v>0.04820371519783762</v>
+        <v>0.0218483456409453</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D18" s="10">
-        <v>0.05120966348683872</v>
+        <v>0.02784706934638893</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01953748942758561</v>
+        <v>0.04173691511555484</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>129</v>
       </c>
       <c r="J18" s="14">
-        <v>0.07520238814540754</v>
+        <v>0.01563502242884445</v>
       </c>
       <c r="K18" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="L18" s="15" t="s">
+      <c r="M18" s="16">
+        <v>0.03970734225116405</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="O18" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="P18" s="18">
+        <v>0.01650881764726816</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="S18" s="16">
+        <v>0.0270471800529162</v>
+      </c>
+      <c r="T18" s="17" t="s">
         <v>136</v>
-      </c>
-      <c r="M18" s="16">
-        <v>0.07528426719719987</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="P18" s="18">
-        <v>0.008372908392253825</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="R18" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="S18" s="16">
-        <v>0.01422538034601543</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>156</v>
       </c>
       <c r="U18" s="17" t="s">
         <v>157</v>
       </c>
       <c r="V18" s="18">
-        <v>0.04226377324878056</v>
+        <v>0.01952225220298305</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02433041788847959</v>
+        <v>0.02051177843269847</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01100288757163998</v>
+        <v>0.03325766002861938</v>
       </c>
       <c r="H19" s="13" t="s">
         <v>130</v>
@@ -2253,333 +2250,333 @@
         <v>131</v>
       </c>
       <c r="J19" s="14">
-        <v>0.06959321088443571</v>
+        <v>0.01339570355798797</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="L19" s="15" t="s">
         <v>137</v>
       </c>
       <c r="M19" s="16">
-        <v>0.04661633732173159</v>
+        <v>0.0216029073827977</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P19" s="18">
-        <v>0.006577770234278401</v>
+        <v>0.0152039831896821</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="S19" s="16">
-        <v>0.007967672309398568</v>
+        <v>0.02083627140662124</v>
       </c>
       <c r="T19" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="U19" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="U19" s="17" t="s">
-        <v>159</v>
-      </c>
       <c r="V19" s="18">
-        <v>0.03245997838337202</v>
+        <v>0.01640965080488664</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D20" s="10">
-        <v>0.0114385807287253</v>
+        <v>0.019803229908905</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G20" s="12">
-        <v>0.009127835677810206</v>
+        <v>0.02324801840813429</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>132</v>
       </c>
       <c r="J20" s="14">
-        <v>0.05586616777962992</v>
+        <v>0.012516476124149</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M20" s="16">
-        <v>0.0192919339665784</v>
+        <v>0.01979373160051502</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P20" s="18">
-        <v>0.006439079698717644</v>
+        <v>0.01337128599033237</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="S20" s="16">
-        <v>0.007718418473549708</v>
+        <v>0.01651242993655088</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02267682724952916</v>
+        <v>0.01383536412732961</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>161</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="D30" s="19" t="s">
         <v>164</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C31" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="C31" s="21" t="s">
-        <v>172</v>
-      </c>
       <c r="D31" s="22">
-        <v>0.2810225764661115</v>
+        <v>0.3421945519030701</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="21" t="s">
-        <v>174</v>
-      </c>
       <c r="D32" s="22">
-        <v>0.2683420172531186</v>
+        <v>0.3397658331900246</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="21" t="s">
-        <v>176</v>
-      </c>
       <c r="D33" s="22">
-        <v>0.03839375929532636</v>
+        <v>0.07441891888129884</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="C34" s="21" t="s">
-        <v>178</v>
-      </c>
       <c r="D34" s="22">
-        <v>0.02126073972245526</v>
+        <v>0.0452331511696961</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="C35" s="21" t="s">
-        <v>180</v>
-      </c>
       <c r="D35" s="22">
-        <v>0.01965086957400864</v>
+        <v>0.04127681215411815</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="C36" s="21" t="s">
-        <v>182</v>
-      </c>
       <c r="D36" s="22">
-        <v>0.01884194032919096</v>
+        <v>0.03083332231684588</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="C37" s="21" t="s">
-        <v>184</v>
-      </c>
       <c r="D37" s="22">
-        <v>0.01470053216865937</v>
+        <v>0.02591026585454881</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="C38" s="21" t="s">
-        <v>186</v>
-      </c>
       <c r="D38" s="22">
-        <v>0.01386158431439583</v>
+        <v>0.02282563093130676</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C39" s="21" t="s">
-        <v>188</v>
-      </c>
       <c r="D39" s="22">
-        <v>0.00911989785412399</v>
+        <v>0.0212743629249443</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="C40" s="21" t="s">
-        <v>190</v>
-      </c>
       <c r="D40" s="22">
-        <v>0.008048310653340478</v>
+        <v>0.02076168413365771</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="C41" s="21" t="s">
-        <v>192</v>
-      </c>
       <c r="D41" s="22">
-        <v>0.007622696927328866</v>
+        <v>0.01881602850258935</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="C42" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="C42" s="21" t="s">
-        <v>194</v>
-      </c>
       <c r="D42" s="22">
-        <v>0.00522537732698064</v>
+        <v>0.01366301778826966</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="C43" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C43" s="21" t="s">
-        <v>196</v>
-      </c>
       <c r="D43" s="22">
-        <v>0.001389193572811634</v>
+        <v>0.002240770950854621</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="C44" s="21" t="s">
-        <v>198</v>
-      </c>
       <c r="D44" s="22">
-        <v>0.0002377329854351124</v>
+        <v>0.0007856492987752822</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C45" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="D45" s="20" t="s">
         <v>200</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2958,331 +2955,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1128022431960192</v>
+        <v>0.198443951387878</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G9" s="12">
-        <v>0.3761816530953212</v>
+        <v>0.2052420042097953</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1344741586036068</v>
+        <v>0.1575906381924479</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1387918614671608</v>
+        <v>0.1929965003205228</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P9" s="18">
-        <v>0.07864811734802314</v>
+        <v>0.1666524790779688</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="S9" s="16">
-        <v>0.6840566446004295</v>
+        <v>0.1806638303978657</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="V9" s="18">
-        <v>0.127850974082602</v>
+        <v>0.1976451408314087</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D10" s="10">
-        <v>0.1108371821224291</v>
+        <v>0.1416443041380451</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1851930918182796</v>
+        <v>0.109365612101175</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J10" s="14">
-        <v>0.08471603410318546</v>
+        <v>0.1329312338108126</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M10" s="16">
-        <v>0.1175224452322718</v>
+        <v>0.1081876117122376</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P10" s="18">
-        <v>0.03744259449254504</v>
+        <v>0.157469790903169</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="S10" s="16">
-        <v>0.05967780361343906</v>
+        <v>0.129307751241627</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1043621549005275</v>
+        <v>0.1961947575275767</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D11" s="10">
-        <v>0.03569192476924938</v>
+        <v>0.04119375600672542</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G11" s="12">
-        <v>0.01836814638376558</v>
+        <v>0.02712329283043233</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J11" s="14">
-        <v>0.04162906410925425</v>
+        <v>0.04366147834343725</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M11" s="16">
-        <v>0.06258522543012041</v>
+        <v>0.06439473786485103</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P11" s="18">
-        <v>0.02624267979051585</v>
+        <v>0.05024717530551617</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="S11" s="16">
-        <v>0.02170828522465099</v>
+        <v>0.03419155792284736</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="V11" s="18">
-        <v>0.05824543615322136</v>
+        <v>0.03667827386387902</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01216086211072519</v>
+        <v>0.02087592800472833</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01264451118149212</v>
+        <v>0.02336133949129239</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J12" s="14">
-        <v>0.0223348550702193</v>
+        <v>0.0324044751335321</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="M12" s="16">
-        <v>0.05443128974705369</v>
+        <v>0.04300582553187905</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P12" s="18">
-        <v>0.009227530784510078</v>
+        <v>0.0343437919348621</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02129370980054375</v>
+        <v>0.01336851358564498</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01779306984196702</v>
+        <v>0.02216448219610231</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D13" s="10">
-        <v>0.009272990499261577</v>
+        <v>0.009163282380408939</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G13" s="12">
-        <v>0.007562455513813342</v>
+        <v>0.02256746389373391</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01915456181756157</v>
+        <v>0.02863662142393738</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M13" s="16">
-        <v>0.007579681643800691</v>
+        <v>0.01200802044156005</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P13" s="18">
-        <v>0.00816673051546014</v>
+        <v>0.01924249630776335</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01689213806711696</v>
+        <v>0.01275958301525208</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01540538879087095</v>
+        <v>0.02045388602977987</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3293,7 +3290,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3302,7 +3299,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3311,7 +3308,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3320,7 +3317,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3329,7 +3326,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3338,7 +3335,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3347,7 +3344,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3356,331 +3353,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D16" s="10">
-        <v>0.5066173155474019</v>
+        <v>0.2658132525652714</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G16" s="12">
-        <v>0.220397766121312</v>
+        <v>0.1773071523928548</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J16" s="14">
-        <v>0.2403755203592911</v>
+        <v>0.2479848189225976</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M16" s="16">
-        <v>0.257472891734414</v>
+        <v>0.1845176449557083</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P16" s="18">
-        <v>0.7531652335008889</v>
+        <v>0.1648125729677172</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="S16" s="16">
-        <v>0.0564601172839742</v>
+        <v>0.2422475477618236</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="V16" s="18">
-        <v>0.2696037345644758</v>
+        <v>0.1664920490503978</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1352587799498013</v>
+        <v>0.1323294900859862</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G17" s="12">
-        <v>0.08015595706217912</v>
+        <v>0.1487131106248561</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J17" s="14">
-        <v>0.2290679695667724</v>
+        <v>0.1652845857871258</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M17" s="16">
-        <v>0.2026686040551678</v>
+        <v>0.1729352930862704</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P17" s="18">
-        <v>0.02941488798664136</v>
+        <v>0.1582009285071977</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="S17" s="16">
-        <v>0.0468072022880441</v>
+        <v>0.1830867443059413</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1525862140427576</v>
+        <v>0.1620790920463926</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D18" s="10">
-        <v>0.0232438395445453</v>
+        <v>0.03491433349231364</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01838850969695294</v>
+        <v>0.05476528010837606</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J18" s="14">
-        <v>0.05921570413194414</v>
+        <v>0.02942823094632602</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M18" s="16">
-        <v>0.0513461336983785</v>
+        <v>0.04656373378253553</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01021937296208113</v>
+        <v>0.03845363239221148</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S18" s="16">
-        <v>0.01524497658768923</v>
+        <v>0.02855773042346093</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="V18" s="18">
-        <v>0.09049308543592871</v>
+        <v>0.03845674721763194</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D19" s="10">
-        <v>0.01654531963037856</v>
+        <v>0.02698299736497644</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01295701255212259</v>
+        <v>0.03913050531081797</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J19" s="14">
-        <v>0.02979225841223217</v>
+        <v>0.02728924142424447</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M19" s="16">
-        <v>0.02177921396936144</v>
+        <v>0.03409519846695891</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P19" s="18">
-        <v>0.005529908323178368</v>
+        <v>0.02704422885340374</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01212185826921557</v>
+        <v>0.02783125919158856</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02436552065947329</v>
+        <v>0.02142221696192899</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D20" s="10">
-        <v>0.004135151603571003</v>
+        <v>0.02250200412339661</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01072125320025244</v>
+        <v>0.03492061597206594</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J20" s="14">
-        <v>0.02725516018960251</v>
+        <v>0.01698842349278329</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01766492874251738</v>
+        <v>0.02253958851049362</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P20" s="18">
-        <v>0.004717817724032954</v>
+        <v>0.02594835278691734</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="S20" s="16">
-        <v>0.01055571127007325</v>
+        <v>0.01621130475931041</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02047263528951246</v>
+        <v>0.01566273723062437</v>
       </c>
     </row>
   </sheetData>
